--- a/.cursor/scratch/tax_turbo_parts/Personal Income 2025.tiny.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/Personal Income 2025.tiny.xlsx
@@ -13,12 +13,13 @@
     <sheet name="Megan T4" sheetId="9" r:id="rId9"/>
     <sheet name="Investments" sheetId="10" r:id="rId10"/>
     <sheet name="524 Ferdinand Ave, Unit 1" sheetId="11" r:id="rId11"/>
+    <sheet name="2025 Data sources" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
   <si>
     <t xml:space="preserve">2022</t>
   </si>
@@ -326,45 +327,336 @@
     <t xml:space="preserve">Wire</t>
   </si>
   <si>
+    <t xml:space="preserve">Art Sales and Purchases</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales 2022</t>
   </si>
   <si>
+    <t xml:space="preserve">Object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROI (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days in Inventory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Ashanti Wood Fertility Figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live Auctioneers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-28 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hindman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07-13 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Large Maya Hardstone Celt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-05 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Mezcala Stone Figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12-18 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Veracruz Sonriente Figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01-08 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Tairona Metal Tumbaga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four Thracian Gilt-Silver Double ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05-27 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11-12 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Thracian Gilt-Silver Tondo of a...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Pair of Canosan Painted Pottery...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thirteen Saharan Stone Bracelets ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amyas Naegele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-05-11 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquinas Hobor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12-13 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Greek Style Bronze Corinthian H...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11-30 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Mercanti</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales 2023</t>
   </si>
   <si>
+    <t xml:space="preserve">Greek Bronze Cheek Pieces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eBay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12-23 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-05-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egyptian Neolithic Flint Tools (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arte Primitivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apulian Red Figure Fragment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-06-06 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Roman-Style Rock Crystal Amphor...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07-28 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Roman Mosaic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ebay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-10 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-22 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Columbian Jade Earspools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-09 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teo Alabaster Mask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcala Stone Temple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcala Stone Figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREEK BRONZE HELMET OF PHRYGIAN TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bactrian Style Stone Votive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Roman Bronze Knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ebay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-03-03 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06-20 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collection of Cylinder Seals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erdal Dere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-07-28 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Egyptian Cylinder Seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09-22 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09-23 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Collection of Tablets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danny Anavian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-07 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-14 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Gold Coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-16 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felix Brejente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bactrian Chlorite Vessel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12-05 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Egyptian Limestone Head of Hathor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12-16 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harlan J. Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12-01 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native America Banner Stone (Butt...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native America Banner Stone (Anthro)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales 2024</t>
   </si>
   <si>
+    <t xml:space="preserve">A Valdivian Stone Votive Axe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09-27 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-03-15 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Roman Marble Leg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-28 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhiteCube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword 10th Century Viking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zevantiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-20 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-05 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Collection of Cylinder Seal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Roman Glass Beaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-26 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-30 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Egyptian Limestone Head of a P...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-02 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-25 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indus Valley Vessels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-23 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-23 00:00:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sales 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Object</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net Income</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Group of 10 Engraved Gems</t>
   </si>
   <si>
-    <t xml:space="preserve">Erdal Dere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harlan J. Berk</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-02-07 00:00:00</t>
   </si>
   <si>
@@ -407,18 +699,9 @@
     <t xml:space="preserve">Cypriot Bichrome Juglet</t>
   </si>
   <si>
-    <t xml:space="preserve">Live Auctioneers</t>
-  </si>
-  <si>
     <t xml:space="preserve">An Attic Black-Figured Fragment</t>
   </si>
   <si>
-    <t xml:space="preserve">Hindman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-05-25 00:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Luristan Bronze Ibex</t>
   </si>
   <si>
@@ -440,15 +723,9 @@
     <t xml:space="preserve">Roman Marble Base with Foot</t>
   </si>
   <si>
-    <t xml:space="preserve">Arte Primitivo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Neolithic Flint Celt</t>
   </si>
   <si>
-    <t xml:space="preserve">2022-12-13 00:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Neolithic Danish Chert Adze</t>
   </si>
   <si>
@@ -470,10 +747,10 @@
     <t xml:space="preserve">2025-01-10 00:00:00</t>
   </si>
   <si>
-    <t xml:space="preserve">Three Ancient Mosaics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamal Rifai and Antiquarium</t>
+    <t xml:space="preserve">Two mosaic deals (EOEB 2/21 pooled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamal Rifai (Deal A) + Plutus/Ant...</t>
   </si>
   <si>
     <t xml:space="preserve">2025-02-21 00:00:00</t>
@@ -482,6 +759,9 @@
     <t xml:space="preserve">Jonathan Yantis</t>
   </si>
   <si>
+    <t xml:space="preserve">UNLOCKED 2026-09-21 40/50 mix. TW...</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canosan Terracotta Horse</t>
   </si>
   <si>
@@ -500,12 +780,63 @@
     <t xml:space="preserve">Books (titles TBD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aquinas Hobor</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-02-04 00:00:00</t>
   </si>
   <si>
+    <t xml:space="preserve">LOCKED 2026-09-20: book SALE $1,0...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Gold Belt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortuna / Erdal Dere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-21 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-15 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCKED 2026-09-21 SALE. Bought Fo...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronze head of a goddess, likely ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-09 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-24 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCKED 2026-09-21 joint SALE (EPG...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALE (joint, EPGC share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">August Fortuna joint — unnamed ob...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-15 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-09 00:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercury 8291 MATCHED/LOCKED: Berk...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art Purchases/Inventory</t>
+  </si>
+  <si>
     <t xml:space="preserve">GCM Boards 2022</t>
   </si>
   <si>
@@ -612,6 +943,114 @@
   </si>
   <si>
     <t xml:space="preserve">OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW THIS FILE IS MADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is last year's Personal Inco...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last year file (model)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drive Personal Income.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1qdewbEnTuc-DXdbqBmwHrKMetGm3I7Zo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132,313 bytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unchanged 2023|2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Income 2025.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copy of that workbook + 2025 columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same 11 tab names and order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hindman actual I4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70,618.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monarch paycheck cash (not W-2 Bo...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YELLOW — Box 1 still ASK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216 Oak Park I5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19,500.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joint 0203 Delach + Ava + Joan cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">524 #2 STR I6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,086.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airbnb/VRBO platform net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCM Boards I7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21,500.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Form 1099-NEC BOM PAYMEN (persona...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art Sales net I8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39,055.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prior MATCHED $23,055.06 + Belt n...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOCKED green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216 Oak Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as Income I5. Vacant Oct + h...</t>
   </si>
 </sst>
 </file>
@@ -843,8 +1282,8 @@
       <c r="H8">
         <v>20000</v>
       </c>
-      <c r="I8" s="3">
-        <v>23055.06</v>
+      <c r="I8" s="2">
+        <v>39055.06</v>
       </c>
     </row>
     <row r="9">
@@ -901,7 +1340,7 @@
       </c>
       <c r="I10" s="4">
         <f>SUM(I4:I9)</f>
-        <v>151760</v>
+        <v>167760</v>
       </c>
     </row>
   </sheetData>
@@ -913,34 +1352,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>290</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>292</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>292</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>295</v>
       </c>
       <c r="B5" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6">
@@ -981,12 +1420,12 @@
         <v>29</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>187</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>298</v>
       </c>
       <c r="J7">
         <v>-9000</v>
@@ -1006,7 +1445,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>299</v>
       </c>
       <c r="M8">
         <v>8000</v>
@@ -1017,7 +1456,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="J9" s="2">
         <v>-9000</v>
@@ -1037,7 +1476,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -1055,10 +1494,10 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>302</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>192</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
@@ -1412,7 +1851,7 @@
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>193</v>
+        <v>303</v>
       </c>
       <c r="O17" s="1">
         <f>SUM(C17:N17)</f>
@@ -1639,7 +2078,7 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>194</v>
+        <v>304</v>
       </c>
       <c r="O25" s="1">
         <f>SUM(C25:N25)</f>
@@ -1652,7 +2091,7 @@
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>195</v>
+        <v>305</v>
       </c>
       <c r="O26" s="1">
         <f>SUM(C26:N26)</f>
@@ -1830,7 +2269,7 @@
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>196</v>
+        <v>306</v>
       </c>
       <c r="J36">
         <v>145</v>
@@ -1846,7 +2285,7 @@
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="O37" s="1">
         <f>SUM(C37:N37)</f>
@@ -1859,7 +2298,7 @@
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>197</v>
+        <v>307</v>
       </c>
       <c r="O38" s="1">
         <f>SUM(C38:N38)</f>
@@ -2044,6 +2483,177 @@
   <mergeCells count="2">
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="P1:AB1"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>332</v>
+      </c>
+      <c r="C9" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" t="s">
+        <v>337</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -5795,8 +6405,14 @@
       <c r="C53">
         <v>136000</v>
       </c>
+      <c r="H53" s="2">
+        <v>76000</v>
+      </c>
+      <c r="K53" s="2">
+        <v>25000</v>
+      </c>
       <c r="N53">
-        <v>150000</v>
+        <v>251000</v>
       </c>
     </row>
     <row r="54">
@@ -5840,7 +6456,7 @@
       </c>
       <c r="H55" s="4">
         <f>SUM(H53:H54)</f>
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="I55" s="4">
         <f>SUM(I53:I54)</f>
@@ -5852,7 +6468,7 @@
       </c>
       <c r="K55" s="4">
         <f>SUM(K53:K54)</f>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="L55" s="4">
         <f>SUM(L53:L54)</f>
@@ -5864,7 +6480,7 @@
       </c>
       <c r="N55" s="4">
         <f>SUM(N53:N54)</f>
-        <v>163595</v>
+        <v>264595</v>
       </c>
     </row>
     <row r="57">
@@ -6238,9 +6854,309 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4">
+        <v>450</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5">
+        <v>906.37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5">
+        <v>1000</v>
+      </c>
+      <c r="G5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5">
+        <v>93.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6">
+        <v>239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6">
+        <v>400</v>
+      </c>
+      <c r="G6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7">
+        <v>900</v>
+      </c>
+      <c r="D7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7">
+        <v>1100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <v>172</v>
+      </c>
+      <c r="D8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8">
+        <v>375</v>
+      </c>
+      <c r="G8" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9">
+        <v>400</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10">
+        <v>375</v>
+      </c>
+      <c r="D10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>700</v>
+      </c>
+      <c r="G10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11">
+        <v>6250</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11">
+        <v>15000</v>
+      </c>
+      <c r="G11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12">
+        <v>6100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12">
+        <v>8000</v>
+      </c>
+      <c r="G12" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13">
+        <v>5250.97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13">
+        <v>9000</v>
+      </c>
+      <c r="G13" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13">
+        <v>3749.03</v>
       </c>
     </row>
     <row r="14">
@@ -6259,7 +7175,556 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17">
+        <v>2870.43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17">
+        <v>8500</v>
+      </c>
+      <c r="G17" t="s">
+        <v>143</v>
+      </c>
+      <c r="H17">
+        <v>5629.57</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18">
+        <v>392.14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18">
+        <v>2500</v>
+      </c>
+      <c r="G18" t="s">
+        <v>143</v>
+      </c>
+      <c r="H18">
+        <v>2107.86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19">
+        <v>750</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19">
+        <v>600</v>
+      </c>
+      <c r="G19" t="s">
+        <v>143</v>
+      </c>
+      <c r="H19">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20">
+        <v>1351.78</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20">
+        <v>1900</v>
+      </c>
+      <c r="G20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20">
+        <v>548.22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21">
+        <v>3938</v>
+      </c>
+      <c r="D21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" t="s">
+        <v>147</v>
+      </c>
+      <c r="F21">
+        <v>8500</v>
+      </c>
+      <c r="G21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22">
+        <v>233</v>
+      </c>
+      <c r="D22" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F22">
+        <v>500</v>
+      </c>
+      <c r="G22" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23">
+        <v>701.5</v>
+      </c>
+      <c r="D23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F23">
+        <v>2000</v>
+      </c>
+      <c r="G23" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23">
+        <v>1298.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24">
+        <v>233</v>
+      </c>
+      <c r="D24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25">
+        <v>233</v>
+      </c>
+      <c r="D25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25">
+        <v>500</v>
+      </c>
+      <c r="G25" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26">
+        <v>2000</v>
+      </c>
+      <c r="D26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26">
+        <v>7000</v>
+      </c>
+      <c r="G26" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27">
+        <v>990</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
+        <v>147</v>
+      </c>
+      <c r="F27">
+        <v>1000</v>
+      </c>
+      <c r="G27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>164</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28" t="s">
+        <v>166</v>
+      </c>
+      <c r="H28">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>167</v>
+      </c>
+      <c r="B29" t="s">
+        <v>168</v>
+      </c>
+      <c r="C29">
+        <v>360000</v>
+      </c>
+      <c r="D29" t="s">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29">
+        <v>410000</v>
+      </c>
+      <c r="G29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H29">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30">
+        <v>3600</v>
+      </c>
+      <c r="D30" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30">
+        <v>4000</v>
+      </c>
+      <c r="G30" t="s">
+        <v>172</v>
+      </c>
+      <c r="H30">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31">
+        <v>45000</v>
+      </c>
+      <c r="D31" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31">
+        <v>55000</v>
+      </c>
+      <c r="G31" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32">
+        <v>4000</v>
+      </c>
+      <c r="D32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32">
+        <v>4700</v>
+      </c>
+      <c r="G32" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33">
+        <v>2000</v>
+      </c>
+      <c r="G33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H33">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34">
+        <v>1000</v>
+      </c>
+      <c r="G34" t="s">
+        <v>185</v>
+      </c>
+      <c r="H34">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>183</v>
+      </c>
+      <c r="E35" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35" t="s">
+        <v>185</v>
+      </c>
+      <c r="H35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36" t="s">
+        <v>185</v>
+      </c>
+      <c r="H36">
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -6278,7 +7743,218 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
         <v>104</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40">
+        <v>470</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40">
+        <v>600</v>
+      </c>
+      <c r="G40" t="s">
+        <v>191</v>
+      </c>
+      <c r="H40">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41">
+        <v>2500</v>
+      </c>
+      <c r="D41" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" t="s">
+        <v>194</v>
+      </c>
+      <c r="F41">
+        <v>2982</v>
+      </c>
+      <c r="G41" t="s">
+        <v>193</v>
+      </c>
+      <c r="H41">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42">
+        <v>1416.99</v>
+      </c>
+      <c r="D42" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42">
+        <v>6500</v>
+      </c>
+      <c r="G42" t="s">
+        <v>198</v>
+      </c>
+      <c r="H42">
+        <v>5083.01</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43">
+        <v>33000</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F43">
+        <v>36000</v>
+      </c>
+      <c r="G43" t="s">
+        <v>200</v>
+      </c>
+      <c r="H43">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B44" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44">
+        <v>25000</v>
+      </c>
+      <c r="D44" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44">
+        <v>37500</v>
+      </c>
+      <c r="G44" t="s">
+        <v>203</v>
+      </c>
+      <c r="H44">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>204</v>
+      </c>
+      <c r="B45" t="s">
+        <v>114</v>
+      </c>
+      <c r="C45">
+        <v>1885.96</v>
+      </c>
+      <c r="D45" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" t="s">
+        <v>184</v>
+      </c>
+      <c r="F45">
+        <v>5500</v>
+      </c>
+      <c r="G45" t="s">
+        <v>206</v>
+      </c>
+      <c r="H45">
+        <v>3614.04</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>207</v>
+      </c>
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C46">
+        <v>214.99</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46">
+        <v>1700</v>
+      </c>
+      <c r="G46" t="s">
+        <v>209</v>
+      </c>
+      <c r="H46">
+        <v>1485.01</v>
       </c>
     </row>
     <row r="47">
@@ -6297,391 +7973,394 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>94</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>111</v>
+      <c r="K50" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C51">
         <v>1000</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G51" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C52">
         <v>300</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G52" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>214</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C53">
         <v>300</v>
       </c>
       <c r="E53" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G53" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>217</v>
       </c>
       <c r="C54">
         <v>1000</v>
       </c>
       <c r="E54" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G54" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C55">
         <v>1000</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G55" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C56">
         <v>1000</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G56" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C57">
         <v>600</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G57" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>124</v>
+        <v>221</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C58">
         <v>600</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G58" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>125</v>
+        <v>222</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C59">
         <v>1000</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G59" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C60">
         <v>4000</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G60" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C61">
         <v>600</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G61" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C62">
         <v>334.44</v>
       </c>
       <c r="D62" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G62" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>133</v>
+        <v>227</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C63">
         <v>234.44</v>
       </c>
       <c r="D63" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G63" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C64">
         <v>2228.76</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G64" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>229</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C65">
         <v>1000</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G65" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="C66">
         <v>4500</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
+        <v>232</v>
       </c>
       <c r="E66" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G66" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C67">
         <v>500</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G67" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C68">
         <v>195.78</v>
       </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G68" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C69">
         <v>311.25</v>
       </c>
       <c r="D69" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G69" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C70">
         <v>2240.27</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>238</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="G70" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71">
@@ -6693,7 +8372,7 @@
         <v>30000</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
       <c r="H71">
         <v>7055.06</v>
@@ -6701,25 +8380,25 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="C73" s="2">
         <v>13000</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="F73" s="2">
         <v>14000</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="H73">
         <v>1000</v>
@@ -6727,42 +8406,45 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="B74" t="s">
-        <v>151</v>
-      </c>
-      <c r="C74" s="2">
+        <v>243</v>
+      </c>
+      <c r="C74" s="3">
         <v>90000</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="E74" t="s">
-        <v>153</v>
+        <v>245</v>
       </c>
       <c r="F74" s="2">
         <v>105000</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>244</v>
       </c>
       <c r="H74">
         <v>15000</v>
       </c>
+      <c r="I74" s="3" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C75">
         <v>900</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="F75">
         <v>1000</v>
@@ -6773,48 +8455,160 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="E76" t="s">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="F76">
         <v>11000</v>
       </c>
       <c r="G76" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>159</v>
+        <v>252</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="F77" s="2">
         <v>1000</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>161</v>
+        <v>253</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
+      <c r="A78" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C78" s="2">
+        <v>45000</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F78" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H78" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C79" s="2">
+        <v>20000</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F79" s="2">
+        <v>26000</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H79" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C80" s="2">
+        <v>20000</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F80" s="2">
+        <v>25000</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H80" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
         <v>76</v>
       </c>
-      <c r="H78" s="4">
-        <f>SUM(H51:H75)</f>
-        <v>23155.06</v>
+      <c r="H81" s="1">
+        <f>SUM(H51:H75)+H78+H79+H80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A82:I82"/>
+  </mergeCells>
 </worksheet>
 </file>
 
@@ -6823,29 +8617,29 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="B4">
         <v>3500</v>
@@ -6862,7 +8656,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="C5">
         <v>2500</v>
@@ -6893,7 +8687,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="E7" s="1">
         <v>25000</v>
@@ -6901,29 +8695,29 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="B11">
         <v>3675</v>
@@ -6957,7 +8751,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="E13" s="1">
         <v>14700</v>
@@ -6965,29 +8759,29 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>172</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="B17">
         <v>4050</v>
@@ -7021,7 +8815,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="E19" s="1">
         <v>16200</v>
@@ -7029,29 +8823,29 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>163</v>
+        <v>273</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="B24">
         <v>4100</v>
@@ -7085,7 +8879,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="E26" s="1">
         <v>21500</v>
@@ -7106,7 +8900,7 @@
   <sheetData>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3">
@@ -7114,26 +8908,26 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -7143,7 +8937,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="E7" s="1">
         <v>115000</v>
@@ -7151,7 +8945,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -7159,26 +8953,26 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13">
@@ -7188,7 +8982,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="E14" s="1">
         <v>110000</v>
@@ -7207,7 +9001,7 @@
   <sheetData>
     <row r="3">
       <c r="A3" t="s">
-        <v>179</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4">
@@ -7215,21 +9009,21 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
       <c r="B5">
         <v>23000</v>
@@ -7263,7 +9057,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="E7" s="1">
         <v>92000</v>
@@ -7271,7 +9065,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -7279,21 +9073,21 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -7303,7 +9097,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="E13" s="1">
         <v>100274</v>
@@ -7311,7 +9105,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16">
@@ -7319,21 +9113,21 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>164</v>
+        <v>274</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>167</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18">
@@ -7343,7 +9137,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
